--- a/Topic Relevant Comments - Nigeria/Shola/7 Women Will Beg One Man to Marry.xlsx
+++ b/Topic Relevant Comments - Nigeria/Shola/7 Women Will Beg One Man to Marry.xlsx
@@ -136,12 +136,12 @@
     <t>Would you like to marry more that one woman? Shola</t>
   </si>
   <si>
+    <t>It's getting really serious right now. At this stage where 2 to 3 women are ready to date a rich man who's capable of providing their immediate needs. We are progressing towards your caption(7 women), and sooner than later, we would all witness the fall of their ego, greed, and shamelessness, which has turned to their wokeness and pride. And when it happens, we are built strong enough to spread our love towards every one of them as men.</t>
+  </si>
+  <si>
     <t>Modern dating's ultimate nightmare disguised as prophecy</t>
   </si>
   <si>
-    <t>It's getting really serious right now. At this stage where 2 to 3 women are ready to date a rich man who's capable of providing their immediate needs. We are progressing towards your caption(7 women), and sooner than later, we would all witness the fall of their ego, greed, and shamelessness, which has turned to their wokeness and pride. And when it happens, we are built strong enough to spread our love towards every one of them as men.</t>
-  </si>
-  <si>
     <t>The problem is that there are not many high value men around, so the few of them get all the pussy. Men need to BALL their SACS up !!!!</t>
   </si>
   <si>
@@ -160,18 +160,18 @@
     <t>Not yet, because if you are not shinning as a man they are not clinging on you...the reality will soon dawn on them though</t>
   </si>
   <si>
+    <t>We the men don't want to talk more about that yet...</t>
+  </si>
+  <si>
     <t>You fools can keep dreaming, women are starting to realize they don't need men en masse, that's the era we're entering</t>
   </si>
   <si>
-    <t>We the men don't want to talk more about that yet...</t>
+    <t>But they won't even be satisfied ever, social media taught them to never settle so each of the 7 women will try to divorce the dude because he "works too much" or because something totally normal he did gave them "the ick", etc If Cristiano Ronaldo's girl is posting thirst traps on IG and Tom Brady's wife divorced him that should tell you everything you need to know They are never, ever satisfied even when given everything and it is entirely social media's fault that they have this insane grass is always greener mindset</t>
   </si>
   <si>
     <t>They go think say na joke. Men are the prize. This girls are just in their era and they feel like all men are after them until they can't even find one. Every man in this world can see a wife to marry no matter how old he is, women can't</t>
   </si>
   <si>
-    <t>But they won't even be satisfied ever, social media taught them to never settle so each of the 7 women will try to divorce the dude because he "works too much" or because something totally normal he did gave them "the ick", etc If Cristiano Ronaldo's girl is posting thirst traps on IG and Tom Brady's wife divorced him that should tell you everything you need to know They are never, ever satisfied even when given everything and it is entirely social media's fault that they have this insane grass is always greener mindset</t>
-  </si>
-  <si>
     <t>Funny how "I don't need a man" turns into "please pick me" when the good ones get scarce. They'll bring their own food, their own clothes, their own peace, just for the privilege of his name. The hunter becomes the hunted. Beautiful.</t>
   </si>
   <si>
@@ -238,12 +238,12 @@
     <t>That era has come n gone already like 2 times(first after world war 1 n Second after world war 2) ...women will adjust. No Dey quote prophet Isaiah wey Dey on colos when he write him scripture</t>
   </si>
   <si>
+    <t>Women don't need men but you papa fuck your mama before you came out to speak this rubbish</t>
+  </si>
+  <si>
     <t>Abeg wise up! Mama dey teach daughter advanced 419 love tactics Fake birthday test to check wallet size? Na red flag factory! If e no hear, pocket go cry blood. Run bros!</t>
   </si>
   <si>
-    <t>Women don't need men but you papa fuck your mama before you came out to speak this rubbish</t>
-  </si>
-  <si>
     <t>Not yet for broke men o. na only man wey guide them dey desperately beg oh</t>
   </si>
   <si>
@@ -256,12 +256,12 @@
     <t>So many chicks I was wooing back then are now coming back to getting it right with me....Maybe they're realising that the chances of marrying a rich man in this country is very low...Some of them are very beautiful, educated but proud and rude.</t>
   </si>
   <si>
+    <t>True got a text from old friend this morning asking about my wellbeing After everything and she is aware that I'm currently in serious relationship Her word Give me a chance let the Gods will happen No be me una wan use HIV kill that was my tot</t>
+  </si>
+  <si>
     <t>It is already happening you just don't notice but men don't call them wives They are addressed as babymama</t>
   </si>
   <si>
-    <t>True got a text from old friend this morning asking about my wellbeing After everything and she is aware that I'm currently in serious relationship Her word Give me a chance let the Gods will happen No be me una wan use HIV kill that was my tot</t>
-  </si>
-  <si>
     <t>Can never be a Godly woman. She knows that God perfects everything in His time. Godly women don't chase, they attract, with value.</t>
   </si>
   <si>
@@ -271,18 +271,21 @@
     <t>I want to marry but it's too expensive..I no fit kill myself</t>
   </si>
   <si>
+    <t>That era don reach since. One even offered me 5M to come marry her</t>
+  </si>
+  <si>
+    <t>Only for rich boys</t>
+  </si>
+  <si>
     <t>That one nah for man wey I guide, you can't really interpret the bible that way</t>
   </si>
   <si>
-    <t>That era don reach since. One even offered me 5M to come marry her</t>
-  </si>
-  <si>
-    <t>Only for rich boys</t>
-  </si>
-  <si>
     <t>For now they're busy flirting with yahoo boys and doing hookups.</t>
   </si>
   <si>
+    <t>They are still looking for rich guys Lol</t>
+  </si>
+  <si>
     <t>My guy we are already in that era as I've witnessed a few</t>
   </si>
   <si>
@@ -301,21 +304,21 @@
     <t>Bible don talk am now</t>
   </si>
   <si>
+    <t>It's happening already, two friends were begging one man to them.</t>
+  </si>
+  <si>
+    <t>This era will come after the death of the simp era,</t>
+  </si>
+  <si>
+    <t>Bible no dey lie. E don dey happen before our eyes</t>
+  </si>
+  <si>
+    <t>Polygamy is gonna be a hot cake</t>
+  </si>
+  <si>
     <t>You're more f**lish Were you the one that wrote it in the bible? You don't even have power over your life talkless of rewriting what has been written in the bible, it's a prophecy and watch it happen.</t>
   </si>
   <si>
-    <t>It's happening already, two friends were begging one man to them.</t>
-  </si>
-  <si>
-    <t>This era will come after the death of the simp era,</t>
-  </si>
-  <si>
-    <t>Bible no dey lie. E don dey happen before our eyes</t>
-  </si>
-  <si>
-    <t>Polygamy is gonna be a hot cake</t>
-  </si>
-  <si>
     <t>Sorry if I can provide and feed myself why will I beg for a surname??? What will it do for me? You guys are living in delulu world.</t>
   </si>
   <si>
@@ -331,15 +334,15 @@
     <t>Not a poor man though</t>
   </si>
   <si>
-    <t>That shxt ain't gonna happen. The people who wrote the Bible were on Colos</t>
-  </si>
-  <si>
     <t>They called me a mad man when mentioned this to some female friends last month...</t>
   </si>
   <si>
     <t>In just less than 3 months since the beginning of 2026, I've rejected 9 of them who've actually forced themselves to be in a relationship with me. At some point you feel like disappearing because they won't even want you to leave once they meet you anywhere. Especially those 30+</t>
   </si>
   <si>
+    <t>Simp still exists</t>
+  </si>
+  <si>
     <t>Sure. Wahala for who know dey read Bible</t>
   </si>
   <si>
@@ -379,12 +382,12 @@
     <t>Same as men desperately looking for women to call their own. This happens in both ways.</t>
   </si>
   <si>
+    <t>There is already 7 women for 1 men. I can relate but you won't believe me. If you only count only the kind of men women like and I'll be nice: no kids, never married, min 5'10, min 8/10 SMV, min 50k/year, bmi&lt;25, single, not even counting fit, his house, car, famous...there is</t>
+  </si>
+  <si>
     <t>What makes you think so... From the beginning of time, there have always been more women than men. Divine ordinances will always ensure that every has a partner</t>
   </si>
   <si>
-    <t>There is already 7 women for 1 men. I can relate but you won't believe me. If you only count only the kind of men women like and I'll be nice: no kids, never married, min 5'10, min 8/10 SMV, min 50k/year, bmi&lt;25, single, not even counting fit, his house, car, famous...there is</t>
-  </si>
-  <si>
     <t>This must be location based cos there was never a time we've had shortage of women</t>
   </si>
   <si>
@@ -421,12 +424,12 @@
     <t>Lol very true, men who are wise and patient will have options, and women who truly value commitment will compete to prove themselves</t>
   </si>
   <si>
+    <t>Have been saying this since last year, the next five years will be cr@zy. Women will be the one chasing while men will be the one running away</t>
+  </si>
+  <si>
     <t>I have been thinking at the rate which the men are die.. through been the outlaw. Some women might consider paying our dowry. I won't go further.</t>
   </si>
   <si>
-    <t>Have been saying this since last year, the next five years will be cr@zy. Women will be the one chasing while men will be the one running away</t>
-  </si>
-  <si>
     <t>@grok gives us analysis of the percentage of women over men in the world</t>
   </si>
   <si>
@@ -487,9 +490,6 @@
     <t>women in 2005 said this same exact shit. The only one here deceiving themselves is you.</t>
   </si>
   <si>
-    <t>Are you more Godly than these</t>
-  </si>
-  <si>
     <t>Are you sure cos I see a lot of single fathers these days</t>
   </si>
   <si>
@@ -568,9 +568,6 @@
     <t>Bible said it</t>
   </si>
   <si>
-    <t>This says otherwise</t>
-  </si>
-  <si>
     <t>No lies bro I said I'm not paying Bride price Again</t>
   </si>
   <si>
@@ -592,9 +589,6 @@
     <t>It is in the Bible</t>
   </si>
   <si>
-    <t>Ok by me, but no fatties girls, take care of yourself for me.</t>
-  </si>
-  <si>
     <t>God doesn't lie!</t>
   </si>
   <si>
@@ -604,7 +598,7 @@
     <t>True It will happen because the Bible said it</t>
   </si>
   <si>
-    <t>FEED YOUR EYES MORE!!!! One thing is certain. REALITY always win over DELUSION!!</t>
+    <t>Just imagine men starts refusing to donate their sperms, there's definitely gonna be a World War</t>
   </si>
   <si>
     <t>The Quran said it too</t>
@@ -617,6 +611,12 @@
   </si>
   <si>
     <t>Bible said it thousand years ago.</t>
+  </si>
+  <si>
+    <t>Everything is happening now, bro. Everything wrote in the Bible is coming to reality ✨️</t>
+  </si>
+  <si>
+    <t>Economy hard fr</t>
   </si>
 </sst>
 </file>
